--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487046_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487046_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7095</v>
+        <v>6.4934</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8388</v>
+        <v>8.537100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1293</v>
+        <v>-2.0437</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7685</v>
+        <v>9.2011</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1365</v>
+        <v>0.7079</v>
       </c>
       <c r="I2" t="n">
-        <v>1.905</v>
+        <v>8.4933</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9313</v>
+        <v>11.3709</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4011</v>
+        <v>3.793</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5302</v>
+        <v>7.5779</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1627</v>
+        <v>-2.1697</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5376</v>
+        <v>-3.0851</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3748</v>
+        <v>0.9154</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1231</v>
+        <v>-3.6672</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2618</v>
+        <v>0.3876</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0656</v>
+        <v>0.1917</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1963</v>
+        <v>0.1959</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5561</v>
+        <v>0.5717</v>
       </c>
       <c r="W2" t="n">
-        <v>1.842</v>
+        <v>1.7997</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1513</v>
+        <v>6.1315</v>
       </c>
       <c r="E3" t="n">
-        <v>8.061199999999999</v>
+        <v>6.3946</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9099</v>
+        <v>-0.2631</v>
       </c>
       <c r="G3" t="n">
-        <v>9.2011</v>
+        <v>1.7685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7079</v>
+        <v>-0.1365</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4933</v>
+        <v>1.905</v>
       </c>
       <c r="J3" t="n">
-        <v>11.3709</v>
+        <v>3.9313</v>
       </c>
       <c r="K3" t="n">
-        <v>3.793</v>
+        <v>2.4011</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5779</v>
+        <v>1.5302</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1697</v>
+        <v>-2.1627</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.0851</v>
+        <v>-2.5376</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9154</v>
+        <v>0.3748</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.6672</v>
+        <v>2.1231</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0456</v>
+        <v>0.6838</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2842</v>
+        <v>0.6214</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3298</v>
+        <v>0.0624</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5717</v>
+        <v>1.5561</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>1.842</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3835</v>
+        <v>2.0686</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3661</v>
+        <v>3.6229</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9826</v>
+        <v>-1.5543</v>
       </c>
       <c r="G4" t="n">
         <v>1.1279</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0073</v>
+        <v>-0.3222</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8196</v>
+        <v>-0.5628</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1877</v>
+        <v>0.2406</v>
       </c>
       <c r="V4" t="n">
         <v>1.842</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0053</v>
+        <v>0.0472</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3265</v>
+        <v>-0.1669</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3212</v>
+        <v>0.2141</v>
       </c>
       <c r="G5" t="n">
         <v>0.4812</v>
@@ -844,13 +844,13 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2935</v>
+        <v>-0.2409</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4164</v>
+        <v>-0.2568</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1229</v>
+        <v>0.0159</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0713</v>
+        <v>-0.1482</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5694</v>
+        <v>-1.5928</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4982</v>
+        <v>1.4446</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2083</v>
@@ -922,13 +922,13 @@
         <v>2.7021</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1488</v>
+        <v>-0.2257</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4132</v>
+        <v>-0.4366</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2644</v>
+        <v>0.2108</v>
       </c>
       <c r="V6" t="n">
         <v>1.5138</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RIASCOS PEREA</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.378</v>
+        <v>-1.1311</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9831</v>
+        <v>-2.2219</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3948</v>
+        <v>1.0908</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5941</v>
+        <v>-1.5617</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9883</v>
+        <v>-2.3329</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3941</v>
+        <v>0.7712</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2938</v>
+        <v>-1.3745</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2938</v>
+        <v>-1.211</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.1635</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3003</v>
+        <v>-0.1872</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6944</v>
+        <v>-1.1219</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3941</v>
+        <v>0.9346</v>
       </c>
       <c r="P7" t="n">
         <v>0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1699</v>
+        <v>0.0446</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3107</v>
+        <v>0.1177</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4805</v>
+        <v>-0.0731</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>J. RIASCOS PEREA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7963</v>
+        <v>-1.4196</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8604</v>
+        <v>-1.1051</v>
       </c>
       <c r="F8" t="n">
-        <v>1.064</v>
+        <v>-0.3145</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5617</v>
+        <v>-1.5941</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3329</v>
+        <v>-1.9883</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7712</v>
+        <v>0.3941</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3745</v>
+        <v>-1.2938</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.211</v>
+        <v>-1.2938</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1635</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1872</v>
+        <v>-0.3003</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1219</v>
+        <v>-0.6944</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9346</v>
+        <v>0.3941</v>
       </c>
       <c r="P8" t="n">
         <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6207</v>
+        <v>-0.2115</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5208</v>
+        <v>0.1887</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0998</v>
+        <v>-0.4002</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.994</v>
+        <v>-2.0238</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9594</v>
+        <v>-0.9624</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0346</v>
+        <v>-1.0614</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5901</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4039</v>
+        <v>-0.4336</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1057</v>
+        <v>-0.1087</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2981</v>
+        <v>-0.3249</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.225</v>
+        <v>-3.6787</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6331</v>
+        <v>-2.1135</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5919</v>
+        <v>-1.5651</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5157</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5162</v>
+        <v>0.0301</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3424</v>
+        <v>0.1772</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1739</v>
+        <v>-0.1471</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6776</v>
+        <v>-5.2681</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6965</v>
+        <v>-5.18</v>
       </c>
       <c r="F11" t="n">
-        <v>0.019</v>
+        <v>-0.0881</v>
       </c>
       <c r="G11" t="n">
         <v>-7.056</v>
@@ -1312,13 +1312,13 @@
         <v>2.7021</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.115</v>
+        <v>0.2945</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6861</v>
+        <v>-0.1695</v>
       </c>
       <c r="U11" t="n">
-        <v>0.571</v>
+        <v>0.464</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2436</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.903199999999999</v>
+        <v>1.071200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.237699999999998</v>
+        <v>5.211999999999998</v>
       </c>
       <c r="F12" t="n">
         <v>-4.1407</v>
@@ -1378,7 +1378,7 @@
         <v>-21.0347</v>
       </c>
       <c r="O12" t="n">
-        <v>4.480099999999999</v>
+        <v>4.4801</v>
       </c>
       <c r="P12" t="n">
         <v>6.661338147750939e-16</v>
@@ -1390,13 +1390,13 @@
         <v>15.4405</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.967900000000001</v>
+        <v>0.006699999999999928</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.2121</v>
+        <v>-0.2376999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2444000000000001</v>
+        <v>0.2442999999999998</v>
       </c>
       <c r="V12" t="n">
         <v>4.012</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8227</v>
+        <v>5.1016</v>
       </c>
       <c r="E13" t="n">
-        <v>8.1968</v>
+        <v>7.3957</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3741</v>
+        <v>-2.2941</v>
       </c>
       <c r="G13" t="n">
         <v>5.203</v>
@@ -1468,13 +1468,13 @@
         <v>2.8951</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7596</v>
+        <v>1.0384</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8567</v>
+        <v>0.0556</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9029</v>
+        <v>0.9829</v>
       </c>
       <c r="V13" t="n">
         <v>-3.0699</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3267</v>
+        <v>3.8653</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1826</v>
+        <v>2.8822</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1441</v>
+        <v>0.9832</v>
       </c>
       <c r="G14" t="n">
         <v>2.1818</v>
@@ -1546,13 +1546,13 @@
         <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5262</v>
+        <v>1.0649</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3226</v>
+        <v>0.0222</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2036</v>
+        <v>1.0427</v>
       </c>
       <c r="V14" t="n">
         <v>2.7418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1756</v>
+        <v>0.8032</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3733</v>
+        <v>2.9741</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1977</v>
+        <v>-2.1709</v>
       </c>
       <c r="G15" t="n">
         <v>0.643</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7991</v>
+        <v>-0.1715</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0417</v>
+        <v>-0.4408</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2426</v>
+        <v>0.2693</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5983</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3333</v>
+        <v>-0.3465</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4095</v>
+        <v>-1.6098</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0762</v>
+        <v>1.2633</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5054999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>2.8951</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8514</v>
+        <v>0.8381</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1891</v>
+        <v>-0.0112</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6623</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.2859</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5314</v>
+        <v>-0.3648</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1897</v>
+        <v>-0.8892</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6582</v>
+        <v>0.5244</v>
       </c>
       <c r="G17" t="n">
         <v>0.1341</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1342</v>
+        <v>0.3007</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6253</v>
+        <v>-0.3249</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7594</v>
+        <v>0.6256</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1857</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.788</v>
+        <v>-0.5565</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4259</v>
+        <v>-1.196</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.362</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1328</v>
+        <v>-0.6646</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1096</v>
+        <v>0.5093</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9768</v>
+        <v>-1.1738</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0599</v>
+        <v>-1.2324</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0764</v>
+        <v>0.0621</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0164</v>
+        <v>-1.2945</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9272</v>
+        <v>0.5679</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0332</v>
+        <v>0.4472</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9604</v>
+        <v>0.1207</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2373</v>
+        <v>0.2009</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4442</v>
+        <v>0.0364</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2069</v>
+        <v>0.1646</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0509</v>
+        <v>-0.8101</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3963</v>
+        <v>-0.8449</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3454</v>
+        <v>0.0347</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6646</v>
+        <v>-1.248</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5093</v>
+        <v>0.4192</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1738</v>
+        <v>-1.6672</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2324</v>
+        <v>-0.8812</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0621</v>
+        <v>0.3726</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2945</v>
+        <v>-1.2538</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5679</v>
+        <v>-0.3668</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4472</v>
+        <v>0.0466</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1207</v>
+        <v>-0.4134</v>
       </c>
       <c r="P19" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2935</v>
+        <v>0.0519</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1639</v>
+        <v>0.0364</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1296</v>
+        <v>0.0155</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1442</v>
+        <v>-0.821</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0451</v>
+        <v>-0.7264</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.248</v>
+        <v>0.1328</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4192</v>
+        <v>1.1096</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6672</v>
+        <v>-0.9768</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8812</v>
+        <v>1.0599</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3726</v>
+        <v>1.0764</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2538</v>
+        <v>-0.0164</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3668</v>
+        <v>-0.9272</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0466</v>
+        <v>0.0332</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4134</v>
+        <v>-0.9604</v>
       </c>
       <c r="P20" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2822</v>
+        <v>0.2042</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1639</v>
+        <v>0.1438</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1183</v>
+        <v>0.0605</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8789</v>
+        <v>-1.2444</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6666</v>
+        <v>-1.1659</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2123</v>
+        <v>-0.0784</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3208</v>
@@ -2092,13 +2092,13 @@
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6233</v>
+        <v>0.0112</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4614</v>
+        <v>0.0393</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.162</v>
+        <v>-0.0281</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6952</v>
+        <v>-3.0561</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4787</v>
+        <v>-2.679</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2165</v>
+        <v>-0.3771</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6085</v>
@@ -2170,13 +2170,13 @@
         <v>0.386</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4574</v>
+        <v>0.0965</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3993</v>
+        <v>0.199</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0581</v>
+        <v>-0.1025</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.9031</v>
+        <v>2.5707</v>
       </c>
       <c r="E23" t="n">
-        <v>4.140900000000001</v>
+        <v>4.1408</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2378</v>
+        <v>-1.57</v>
       </c>
       <c r="G23" t="n">
         <v>2.9473</v>
@@ -2248,13 +2248,13 @@
         <v>15.4406</v>
       </c>
       <c r="S23" t="n">
-        <v>2.968</v>
+        <v>3.6353</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2443</v>
+        <v>-0.2442</v>
       </c>
       <c r="U23" t="n">
-        <v>3.2121</v>
+        <v>3.8798</v>
       </c>
       <c r="V23" t="n">
         <v>-4.012</v>
